--- a/data/attendance/ANNEX_عميرش_3AM.xlsx
+++ b/data/attendance/ANNEX_عميرش_3AM.xlsx
@@ -66,12 +66,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
+          <t>student_id:04d17a60-0813-40ae-a3f1-33a62ac06c1d</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <t>student_id:2948ef82-c8e3-45d2-ab79-a1ee68440a92</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <t>student_id:cd8cdf02-8534-4853-a8d9-84f034f3fffc</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <t>student_id:27180ef1-421c-4e0c-87d6-ad27978db45c</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0">
+      <text>
+        <r>
+          <t>student_id:5d347aef-5a9a-4422-89df-34f611d9020f</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0">
+      <text>
+        <r>
+          <t>student_id:6e5266d4-9159-4383-9c90-1a48e18a241b</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>عميرش 3AM  |  ANNEX  |  3AM  |  عميرش وفاء</t>
   </si>
@@ -85,6 +127,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -94,6 +139,9 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
+    <t>03/10/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -118,6 +166,24 @@
     <t>بن كحمان محمد امير</t>
   </si>
   <si>
+    <t>بن هلال عبد الرحمان</t>
+  </si>
+  <si>
+    <t>سبتي امين</t>
+  </si>
+  <si>
+    <t>مروك صالح</t>
+  </si>
+  <si>
+    <t>مروك زاهر</t>
+  </si>
+  <si>
+    <t>قاولي ندى</t>
+  </si>
+  <si>
+    <t>لمويسي  ايناس</t>
+  </si>
+  <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
   </si>
   <si>
@@ -145,7 +211,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -635,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -661,7 +730,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -671,10 +740,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -716,46 +788,46 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -763,7 +835,7 @@
         <v>502</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -807,7 +879,7 @@
         <v>504</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -851,7 +923,7 @@
         <v>506</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -895,7 +967,7 @@
         <v>507</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -939,7 +1011,7 @@
         <v>508</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" s="8">
         <v>0</v>
@@ -983,7 +1055,7 @@
         <v>509</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" s="9">
         <v>0</v>
@@ -1027,7 +1099,7 @@
         <v>510</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8">
         <v>0</v>
@@ -1063,6 +1135,270 @@
         <v>0</v>
       </c>
       <c r="N11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>906</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>907</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>908</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>909</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>910</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>963</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1082,7 +1418,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -1090,77 +1426,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/data/attendance/ANNEX_عميرش_3AM.xlsx
+++ b/data/attendance/ANNEX_عميرش_3AM.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082C3550-6F76-4D1A-B629-6C20CD791B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
+    <sheet name="Présences" sheetId="1" r:id="rId1"/>
+    <sheet name="📖 Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
   <si>
     <t>عميرش 3AM  |  ANNEX  |  3AM  |  عميرش وفاء</t>
   </si>
@@ -116,46 +120,53 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <b/>
+      <sz val="9"/>
       <color rgb="FFC00000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFC00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="666666"/>
-      <sz val="9"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -228,14 +239,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -258,6 +263,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -596,34 +610,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+    </row>
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -637,617 +651,617 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0</v>
-      </c>
-      <c r="N3" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="C4" s="11">
+        <v>46298</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>216</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="8">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0</v>
-      </c>
-      <c r="F5" s="8">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>217</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="9">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0</v>
-      </c>
-      <c r="F6" s="9">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9">
-        <v>0</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9">
-        <v>0</v>
-      </c>
-      <c r="K6" s="9">
-        <v>0</v>
-      </c>
-      <c r="L6" s="9">
-        <v>0</v>
-      </c>
-      <c r="M6" s="9">
-        <v>0</v>
-      </c>
-      <c r="N6" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>218</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>219</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="9">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9">
-        <v>0</v>
-      </c>
-      <c r="F8" s="9">
-        <v>0</v>
-      </c>
-      <c r="G8" s="9">
-        <v>0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>0</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0</v>
-      </c>
-      <c r="J8" s="9">
-        <v>0</v>
-      </c>
-      <c r="K8" s="9">
-        <v>0</v>
-      </c>
-      <c r="L8" s="9">
-        <v>0</v>
-      </c>
-      <c r="M8" s="9">
-        <v>0</v>
-      </c>
-      <c r="N8" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="C8" s="7">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>220</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="8">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0</v>
-      </c>
-      <c r="F9" s="8">
-        <v>0</v>
-      </c>
-      <c r="G9" s="8">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8">
-        <v>0</v>
-      </c>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8">
-        <v>0</v>
-      </c>
-      <c r="M9" s="8">
-        <v>0</v>
-      </c>
-      <c r="N9" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0</v>
+      </c>
+      <c r="M9" s="6">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>221</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="9">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9">
-        <v>0</v>
-      </c>
-      <c r="F10" s="9">
-        <v>0</v>
-      </c>
-      <c r="G10" s="9">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>0</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0</v>
-      </c>
-      <c r="J10" s="9">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <v>0</v>
-      </c>
-      <c r="L10" s="9">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-      <c r="N10" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>222</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="8">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8">
-        <v>0</v>
-      </c>
-      <c r="M11" s="8">
-        <v>0</v>
-      </c>
-      <c r="N11" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>223</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="9">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0</v>
-      </c>
-      <c r="F12" s="9">
-        <v>0</v>
-      </c>
-      <c r="G12" s="9">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>0</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="9">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9">
-        <v>0</v>
-      </c>
-      <c r="N12" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0</v>
+      </c>
+      <c r="I12" s="7">
+        <v>0</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0</v>
+      </c>
+      <c r="K12" s="7">
+        <v>0</v>
+      </c>
+      <c r="L12" s="7">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7">
+        <v>0</v>
+      </c>
+      <c r="N12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>224</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="8">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0</v>
-      </c>
-      <c r="F13" s="8">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8">
-        <v>0</v>
-      </c>
-      <c r="K13" s="8">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="8">
-        <v>0</v>
-      </c>
-      <c r="N13" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
+        <v>0</v>
+      </c>
+      <c r="L13" s="6">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
         <v>225</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="9">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9">
-        <v>0</v>
-      </c>
-      <c r="F14" s="9">
-        <v>0</v>
-      </c>
-      <c r="G14" s="9">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9">
-        <v>0</v>
-      </c>
-      <c r="I14" s="9">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="C14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7">
+        <v>0</v>
+      </c>
+      <c r="J14" s="7">
+        <v>0</v>
+      </c>
+      <c r="K14" s="7">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7">
+        <v>0</v>
+      </c>
+      <c r="M14" s="7">
+        <v>0</v>
+      </c>
+      <c r="N14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
         <v>226</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="8">
-        <v>0</v>
-      </c>
-      <c r="D15" s="8">
-        <v>0</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0</v>
-      </c>
-      <c r="F15" s="8">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8">
-        <v>0</v>
-      </c>
-      <c r="J15" s="8">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8">
-        <v>0</v>
-      </c>
-      <c r="M15" s="8">
-        <v>0</v>
-      </c>
-      <c r="N15" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6">
+        <v>0</v>
+      </c>
+      <c r="J15" s="6">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0</v>
+      </c>
+      <c r="L15" s="6">
+        <v>0</v>
+      </c>
+      <c r="M15" s="6">
+        <v>0</v>
+      </c>
+      <c r="N15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>227</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="9">
-        <v>0</v>
-      </c>
-      <c r="D16" s="9">
-        <v>0</v>
-      </c>
-      <c r="E16" s="9">
-        <v>0</v>
-      </c>
-      <c r="F16" s="9">
-        <v>0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>0</v>
-      </c>
-      <c r="I16" s="9">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9">
-        <v>0</v>
-      </c>
-      <c r="K16" s="9">
-        <v>0</v>
-      </c>
-      <c r="L16" s="9">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-      <c r="N16" s="9">
+      <c r="C16" s="7">
+        <v>0</v>
+      </c>
+      <c r="D16" s="7">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7">
+        <v>0</v>
+      </c>
+      <c r="I16" s="7">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7">
+        <v>0</v>
+      </c>
+      <c r="K16" s="7">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7">
+        <v>0</v>
+      </c>
+      <c r="N16" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1257,23 +1271,23 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:A16"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1354,6 +1368,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>